--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK41"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45965.41666666666</v>
+        <v>45965.39583333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="19">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>6.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="25">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.88</v>
+        <v>1.35</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="N35" t="n">
-        <v>3.85</v>
+        <v>8.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="N36" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.45</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="M41" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,46 +5739,175 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.63</v>
       </c>
-      <c r="Z41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3" t="n">
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
         <v>2.3</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>6.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6.1</v>
+        <v>1.48</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4793,65 +4793,65 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z34" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.35</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M36" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,14 +5184,14 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N37" t="n">
         <v>3.8</v>
       </c>
-      <c r="N37" t="n">
-        <v>3.85</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.63</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.98</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N40" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="N41" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,135 +5779,6 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>6.1</v>
+        <v>1.48</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>6.9</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1.48</v>
+        <v>6.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.7</v>
+        <v>1.35</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.88</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="N36" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>2.03</v>
       </c>
       <c r="M40" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>8.5</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M41" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK41"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="35">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="M36" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="N37" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N39" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.03</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5779,6 +5779,135 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,14 +5055,14 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N36" t="n">
         <v>3.8</v>
       </c>
-      <c r="N36" t="n">
-        <v>3.85</v>
-      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.45</v>
+        <v>2.7</v>
       </c>
       <c r="M37" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="M40" t="n">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>8.5</v>
+        <v>3.85</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.98</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.9</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>6.1</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>4.8</v>
+        <v>3.62</v>
       </c>
       <c r="N35" t="n">
-        <v>6.6</v>
+        <v>2.79</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="M37" t="n">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.63</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.03</v>
+        <v>1.26</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="N40" t="n">
-        <v>3.85</v>
+        <v>2.61</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="N41" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.35</v>
+        <v>2.12</v>
       </c>
       <c r="M42" t="n">
-        <v>5.1</v>
+        <v>3.98</v>
       </c>
       <c r="N42" t="n">
-        <v>8.5</v>
+        <v>2.88</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>00:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -678,34 +678,34 @@
         <v>4.4</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y2" t="n">
         <v>1.63</v>
@@ -720,10 +720,10 @@
         <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45965.02083333334</v>
+        <v>45965.03125</v>
       </c>
     </row>
     <row r="3">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="N39" t="n">
-        <v>7.1</v>
+        <v>2.61</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="M41" t="n">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="N41" t="n">
-        <v>3.81</v>
+        <v>2.75</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="N42" t="n">
-        <v>2.88</v>
+        <v>7.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="M36" t="n">
-        <v>3.61</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>3.81</v>
+        <v>9.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N38" t="n">
-        <v>9.5</v>
+        <v>3.81</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,55 +5442,55 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z39" t="n">
         <v>2.45</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2</v>
-      </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.39</v>
+        <v>2.12</v>
       </c>
       <c r="M42" t="n">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="N42" t="n">
-        <v>7.1</v>
+        <v>2.88</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="N37" t="n">
-        <v>2.79</v>
+        <v>2.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="N38" t="n">
-        <v>3.81</v>
+        <v>2.79</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.28</v>
+        <v>1.89</v>
       </c>
       <c r="M39" t="n">
-        <v>3.74</v>
+        <v>3.61</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>3.81</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,55 +5700,55 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z41" t="n">
         <v>2.45</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2</v>
-      </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.12</v>
+        <v>1.26</v>
       </c>
       <c r="M42" t="n">
-        <v>3.98</v>
+        <v>6</v>
       </c>
       <c r="N42" t="n">
-        <v>2.88</v>
+        <v>9.5</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>1.39</v>
       </c>
       <c r="M34" t="n">
-        <v>3.19</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.96</v>
+        <v>7.1</v>
       </c>
       <c r="O34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,19 +4864,19 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="M38" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="N38" t="n">
-        <v>2.79</v>
+        <v>3.81</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="M39" t="n">
-        <v>3.61</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
-        <v>3.81</v>
+        <v>9.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="M40" t="n">
-        <v>4.8</v>
+        <v>3.74</v>
       </c>
       <c r="N40" t="n">
-        <v>7.1</v>
+        <v>2.75</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5779,135 +5779,6 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Union Saint-Gilloise</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6</v>
-      </c>
-      <c r="N42" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
         <v>2.15</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45965.03125</v>
+        <v>45965.02083333334</v>
       </c>
     </row>
     <row r="3">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.39</v>
+        <v>2.28</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>3.74</v>
       </c>
       <c r="N34" t="n">
-        <v>7.1</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="M35" t="n">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="N35" t="n">
-        <v>2.88</v>
+        <v>3.81</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="M38" t="n">
-        <v>3.61</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>3.81</v>
+        <v>9.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.26</v>
+        <v>2.12</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>3.98</v>
       </c>
       <c r="N39" t="n">
-        <v>9.5</v>
+        <v>2.88</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="M41" t="n">
-        <v>3.58</v>
+        <v>4.8</v>
       </c>
       <c r="N41" t="n">
-        <v>2.61</v>
+        <v>7.1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.28</v>
+        <v>1.26</v>
       </c>
       <c r="M34" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>9.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.26</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="N38" t="n">
-        <v>9.5</v>
+        <v>2.61</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="M39" t="n">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="N39" t="n">
-        <v>2.88</v>
+        <v>7.1</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,55 +5571,55 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z40" t="n">
         <v>2.45</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2</v>
-      </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="M41" t="n">
-        <v>4.8</v>
+        <v>3.61</v>
       </c>
       <c r="N41" t="n">
-        <v>7.1</v>
+        <v>3.81</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK41"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>00:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45965.02083333334</v>
+        <v>45965.03125</v>
       </c>
     </row>
     <row r="3">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="35">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="N36" t="n">
-        <v>2.79</v>
+        <v>7.1</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N37" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>1.89</v>
       </c>
       <c r="M38" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="N38" t="n">
-        <v>2.61</v>
+        <v>3.81</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="M40" t="n">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="N40" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="M41" t="n">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="N41" t="n">
-        <v>3.81</v>
+        <v>2.88</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5779,6 +5779,135 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="12">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="M32" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="O32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="M36" t="n">
-        <v>4.8</v>
+        <v>3.61</v>
       </c>
       <c r="N36" t="n">
-        <v>7.1</v>
+        <v>3.81</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="M38" t="n">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="N38" t="n">
-        <v>3.81</v>
+        <v>7.1</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="M40" t="n">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="N40" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="M41" t="n">
-        <v>3.98</v>
+        <v>4.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.88</v>
+        <v>5.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N42" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>2.13</v>
       </c>
       <c r="M23" t="n">
-        <v>5.6</v>
+        <v>3.19</v>
       </c>
       <c r="N23" t="n">
-        <v>1.27</v>
+        <v>2.96</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="M26" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.75</v>
+        <v>6.4</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>3.62</v>
       </c>
       <c r="N29" t="n">
-        <v>6.4</v>
+        <v>2.79</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.85</v>
+        <v>1.89</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N30" t="n">
-        <v>2.45</v>
+        <v>3.81</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="M33" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="N33" t="n">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="N34" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.78</v>
+        <v>2.45</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="N36" t="n">
-        <v>3.81</v>
+        <v>2.61</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,780 +5134,6 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>FK Bodo - Glimt</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>København</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N38" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bayern München</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Sheffield United</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Olympiakos Piraeus</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M42" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>1.58</v>
       </c>
       <c r="M23" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
-        <v>2.96</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,19 +3445,19 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>1.27</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,11 +3546,11 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.15</v>
       </c>
-      <c r="Z24" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AA24" t="n">
         <v>0</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>3.19</v>
       </c>
       <c r="N27" t="n">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="M30" t="n">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,11 +4320,11 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z30" t="n">
         <v>1.68</v>
       </c>
-      <c r="Z30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.28</v>
+        <v>2.85</v>
       </c>
       <c r="M31" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M32" t="n">
         <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.39</v>
+        <v>2.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>7.1</v>
+        <v>2.95</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,16 +4836,16 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="35">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N35" t="n">
-        <v>9.5</v>
+        <v>3.81</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5134,6 +5134,780 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M42" t="n">
+        <v>6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -678,34 +678,34 @@
         <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>4.3</v>
+        <v>4.96</v>
       </c>
       <c r="Y2" t="n">
         <v>1.63</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3669,10 +3669,10 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>2.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.19</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="M29" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>6.4</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="N33" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,55 +5055,55 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2.45</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2</v>
-      </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="N37" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="M38" t="n">
-        <v>3.62</v>
+        <v>6</v>
       </c>
       <c r="N38" t="n">
-        <v>2.79</v>
+        <v>9.5</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="M39" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="N39" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="M40" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="N40" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N41" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="M42" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="N42" t="n">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK42"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.58</v>
+        <v>2.8</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>3.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.63</v>
+        <v>1.23</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="M25" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,19 +3832,19 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="27">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="M27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X27" t="n">
         <v>3.4</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Y28" t="n">
         <v>1.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.98</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="N30" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.05</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>9.5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,16 +4449,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>3.81</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="M33" t="n">
-        <v>3.19</v>
+        <v>3.98</v>
       </c>
       <c r="N33" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="O33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,19 +4735,19 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N34" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="35">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="N35" t="n">
-        <v>3.81</v>
+        <v>2.79</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="N36" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>2.45</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5134,780 +5134,6 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>FK Bodo - Glimt</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Union Saint-Gilloise</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M38" t="n">
-        <v>6</v>
-      </c>
-      <c r="N38" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Sheffield United</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M40" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Olympiakos Piraeus</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>København</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N42" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK36"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -696,34 +696,34 @@
         <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>4.96</v>
+        <v>4.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
         <v>1.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45965.03125</v>
+        <v>45965.02083333334</v>
       </c>
     </row>
     <row r="3">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.65</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.85</v>
-      </c>
       <c r="T21" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>3.38</v>
+        <v>2.89</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>2.57</v>
+        <v>2.95</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.32</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,28 +3507,28 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="T24" t="n">
         <v>3.1</v>
@@ -3537,31 +3537,31 @@
         <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>4.03</v>
       </c>
       <c r="O25" t="n">
-        <v>2.95</v>
+        <v>2.44</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
         <v>3.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>4.03</v>
+        <v>6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.3</v>
+        <v>6.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X27" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.54</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="O28" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="N29" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="N31" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.07</v>
+        <v>2.68</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="N32" t="n">
-        <v>3.81</v>
+        <v>2.61</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="M33" t="n">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>2.88</v>
+        <v>3.81</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,16 +4707,16 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="O34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="M35" t="n">
-        <v>3.62</v>
+        <v>4.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>7.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,135 +5005,6 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2616,22 +2616,22 @@
         <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
         <v>5.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
         <v>3.58</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
@@ -2640,7 +2640,7 @@
         <v>1.12</v>
       </c>
       <c r="X17" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="Y17" t="n">
         <v>1.5</v>
@@ -2658,7 +2658,7 @@
         <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
         <v>2.3</v>
@@ -2742,34 +2742,34 @@
         <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
         <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="T18" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="Y18" t="n">
         <v>1.7</v>
@@ -2778,16 +2778,16 @@
         <v>2.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>2.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>3.56</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.54</v>
+        <v>3.07</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
         <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AB22" t="n">
         <v>1.23</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.5</v>
       </c>
-      <c r="O23" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.34</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>2.94</v>
+        <v>3.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.44</v>
+        <v>2.89</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.57</v>
+        <v>3.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
         <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
         <v>3.1</v>
       </c>
       <c r="U24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.32</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="X24" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3636,19 +3636,19 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
         <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>4.03</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>2.44</v>
       </c>
       <c r="P25" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
         <v>4.3</v>
@@ -3663,10 +3663,10 @@
         <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
         <v>1.3</v>
@@ -3675,16 +3675,16 @@
         <v>3.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
         <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
         <v>1.82</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>4.58</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="T26" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.4</v>
       </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.26</v>
-      </c>
       <c r="X26" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.89</v>
+        <v>1.68</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>2.01</v>
+        <v>2.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.25</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X27" t="n">
-        <v>3.62</v>
+        <v>3.38</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>1.26</v>
       </c>
       <c r="M28" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.75</v>
+        <v>9.5</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="M29" t="n">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="N29" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="N30" t="n">
-        <v>9.5</v>
+        <v>2.79</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="O31" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P31" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.35</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
         <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.31</v>
+        <v>2.98</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z32" t="n">
         <v>2.45</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2</v>
-      </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="M33" t="n">
-        <v>3.61</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.81</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="M34" t="n">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="N34" t="n">
-        <v>2.88</v>
+        <v>3.81</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.83</v>
+        <v>2.74</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.91</v>
+        <v>1.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>4.8</v>
+        <v>3.58</v>
       </c>
       <c r="N35" t="n">
-        <v>7.1</v>
+        <v>2.61</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>00:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -696,34 +696,34 @@
         <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="Y2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.57</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
         <v>1.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
         <v>2.25</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45965.02083333334</v>
+        <v>45965.03125</v>
       </c>
     </row>
     <row r="3">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
         <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.05</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T17" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
         <v>2.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>5.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="T18" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X18" t="n">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA18" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.06</v>
+        <v>2.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,31 +3249,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O22" t="n">
-        <v>3.56</v>
+        <v>3.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
         <v>1.34</v>
@@ -3282,28 +3282,28 @@
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,62 +3378,62 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>6.4</v>
+        <v>2.45</v>
       </c>
       <c r="O23" t="n">
-        <v>2.03</v>
+        <v>3.56</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.25</v>
+        <v>3.07</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>3.62</v>
+        <v>2.94</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Z23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD23" t="n">
         <v>2</v>
       </c>
-      <c r="AA23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>6.4</v>
       </c>
       <c r="O24" t="n">
-        <v>3.14</v>
+        <v>2.03</v>
       </c>
       <c r="P24" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>6.25</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
         <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="X24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.89</v>
       </c>
-      <c r="Y24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.44</v>
+        <v>2.59</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.3</v>
+        <v>4.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="T25" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA26" t="n">
         <v>3.45</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.26</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>9.5</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X28" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AB28" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.98</v>
+        <v>3.62</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="O29" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.98</v>
+        <v>3.23</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="U29" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X29" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.62</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.79</v>
+        <v>9.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.23</v>
+        <v>6.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="U30" t="n">
         <v>1.69</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.63</v>
+        <v>1.88</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.39</v>
       </c>
-      <c r="M31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AC31" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.98</v>
+        <v>1.85</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.28</v>
+        <v>1.39</v>
       </c>
       <c r="M32" t="n">
-        <v>3.74</v>
+        <v>4.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>7.1</v>
       </c>
       <c r="O32" t="n">
-        <v>2.69</v>
+        <v>1.91</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>5.75</v>
+        <v>4.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.16</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>2.98</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="P33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.68</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.01</v>
+        <v>3.16</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.31</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
-        <v>3.61</v>
+        <v>3.98</v>
       </c>
       <c r="N34" t="n">
-        <v>3.81</v>
+        <v>2.88</v>
       </c>
       <c r="O34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.57</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="V34" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>3.88</v>
+        <v>7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.74</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="M35" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="N35" t="n">
-        <v>2.61</v>
+        <v>5.3</v>
       </c>
       <c r="O35" t="n">
-        <v>2.8</v>
+        <v>2.11</v>
       </c>
       <c r="P35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2</v>
-      </c>
       <c r="AA35" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>2.31</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1968,28 +1968,28 @@
         <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
         <v>1.5</v>
@@ -1998,16 +1998,16 @@
         <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AA12" t="n">
         <v>5.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
         <v>2.55</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,77 +2862,77 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="S19" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="U19" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.1</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.33</v>
       </c>
-      <c r="AA19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="M20" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S20" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="T20" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.5</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="M21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X21" t="n">
         <v>3.4</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.12</v>
-      </c>
       <c r="Y21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="R22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X22" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N23" t="n">
         <v>2.85</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.45</v>
-      </c>
       <c r="O23" t="n">
-        <v>3.56</v>
+        <v>3.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.07</v>
+        <v>3.44</v>
       </c>
       <c r="R23" t="n">
         <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X23" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3510,19 +3510,19 @@
         <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="O24" t="n">
         <v>2.03</v>
       </c>
       <c r="P24" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.25</v>
+        <v>5.4</v>
       </c>
       <c r="R24" t="n">
         <v>1.33</v>
@@ -3531,7 +3531,7 @@
         <v>3.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
         <v>1.42</v>
@@ -3549,7 +3549,7 @@
         <v>1.8</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
         <v>2.89</v>
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="O25" t="n">
         <v>2.59</v>
@@ -3654,43 +3654,43 @@
         <v>4.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
         <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X25" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
         <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AB25" t="n">
         <v>1.19</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
         <v>1.79</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>2.44</v>
       </c>
       <c r="O26" t="n">
-        <v>2.44</v>
+        <v>3.56</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.3</v>
+        <v>3.07</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X26" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
         <v>3.45</v>
@@ -3909,7 +3909,7 @@
         <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
@@ -3918,7 +3918,7 @@
         <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="U27" t="n">
         <v>1.4</v>
@@ -3933,7 +3933,7 @@
         <v>3.38</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Z27" t="n">
         <v>1.9</v>
@@ -3942,13 +3942,13 @@
         <v>3.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AC27" t="n">
         <v>1.69</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.45</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2</v>
-      </c>
       <c r="AA28" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AC28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="M29" t="n">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="N29" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.23</v>
+        <v>2.98</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N30" t="n">
-        <v>9.5</v>
+        <v>3.81</v>
       </c>
       <c r="O30" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.21</v>
+        <v>2.57</v>
       </c>
       <c r="U30" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>3.88</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.07</v>
+        <v>2.74</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.88</v>
+        <v>2.17</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="N31" t="n">
-        <v>3.81</v>
+        <v>2.79</v>
       </c>
       <c r="O31" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z31" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AA31" t="n">
-        <v>2.74</v>
+        <v>2.19</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.39</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="M32" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="N32" t="n">
-        <v>7.1</v>
+        <v>5.16</v>
       </c>
       <c r="O32" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="P32" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.5</v>
+        <v>5.35</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.98</v>
+        <v>2.2</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>1.26</v>
       </c>
       <c r="M33" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>9.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="R33" t="n">
         <v>1.22</v>
@@ -4692,37 +4692,37 @@
         <v>3.75</v>
       </c>
       <c r="T33" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="U33" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.16</v>
+        <v>1.88</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,62 +4797,62 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="M34" t="n">
-        <v>3.98</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
-        <v>2.88</v>
+        <v>7.1</v>
       </c>
       <c r="O34" t="n">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="P34" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.98</v>
+        <v>6.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="U34" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>7</v>
+        <v>4.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AB34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD34" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.7</v>
+        <v>2.98</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="N35" t="n">
-        <v>5.3</v>
+        <v>2.61</v>
       </c>
       <c r="O35" t="n">
-        <v>2.11</v>
+        <v>2.8</v>
       </c>
       <c r="P35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="R35" t="n">
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.3</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH35" t="n">
-        <v>2.31</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -678,7 +678,7 @@
         <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="P2" t="n">
         <v>2.35</v>
@@ -690,10 +690,10 @@
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
         <v>1.54</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>4.4</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>5.36</v>
       </c>
       <c r="O12" t="n">
         <v>2.45</v>
@@ -1980,31 +1980,31 @@
         <v>1.61</v>
       </c>
       <c r="S12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X12" t="n">
         <v>2.2</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Y12" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="Z12" t="n">
         <v>1.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="AB12" t="n">
         <v>1.11</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
         <v>1.95</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,62 +2604,62 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>2.13</v>
       </c>
       <c r="P17" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>4.85</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>2.3</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O18" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.05</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
         <v>2.8</v>
@@ -2874,46 +2874,46 @@
         <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.58</v>
+        <v>3.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
         <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA19" t="n">
         <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="n">
         <v>1.65</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="O20" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
         <v>1.8</v>
@@ -3015,22 +3015,22 @@
         <v>2.15</v>
       </c>
       <c r="T20" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X20" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="Z20" t="n">
         <v>1.33</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4.08</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="P21" t="n">
         <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="M22" t="n">
         <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.54</v>
+        <v>4.58</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.28</v>
       </c>
-      <c r="X22" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,77 +3378,77 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.3</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
         <v>1.83</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>6</v>
+        <v>2.75</v>
       </c>
       <c r="O24" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W24" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="X24" t="n">
-        <v>3.62</v>
+        <v>2.89</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.89</v>
+        <v>3.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.97</v>
+        <v>2.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.74</v>
+        <v>2.45</v>
       </c>
       <c r="O25" t="n">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.58</v>
+        <v>3.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.31</v>
       </c>
-      <c r="V25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.85</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.56</v>
+        <v>2.02</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.07</v>
+        <v>5.4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>2.94</v>
+        <v>3.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
         <v>3.45</v>
@@ -3906,46 +3906,46 @@
         <v>2.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
         <v>2.73</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X27" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
         <v>1.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AB27" t="n">
         <v>1.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AD27" t="n">
         <v>2.05</v>
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
         <v>1.71</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="O28" t="n">
-        <v>2.69</v>
+        <v>3.15</v>
       </c>
       <c r="P28" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="T28" t="n">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="U28" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
         <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AD28" t="n">
-        <v>3.16</v>
+        <v>2.35</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="M29" t="n">
-        <v>3.98</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>3.81</v>
       </c>
       <c r="O29" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.73</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>3.22</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.83</v>
+        <v>2.83</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="N30" t="n">
-        <v>3.81</v>
+        <v>7.1</v>
       </c>
       <c r="O30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P30" t="n">
         <v>2.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
         <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X30" t="n">
-        <v>3.88</v>
+        <v>4.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,77 +4410,77 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.62</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.79</v>
+        <v>9.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.23</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T31" t="n">
         <v>2.36</v>
       </c>
       <c r="U31" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
         <v>1.1</v>
       </c>
-      <c r="X31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>3.55</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="M32" t="n">
-        <v>4.15</v>
+        <v>3.74</v>
       </c>
       <c r="N32" t="n">
-        <v>5.16</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>2.11</v>
+        <v>2.74</v>
       </c>
       <c r="P32" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X32" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.68</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>9.5</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="P33" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="U33" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.07</v>
+        <v>2.68</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>3.62</v>
       </c>
       <c r="N34" t="n">
-        <v>7.1</v>
+        <v>2.79</v>
       </c>
       <c r="O34" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.5</v>
+        <v>2.97</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U34" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>4.25</v>
+        <v>5.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.98</v>
+        <v>1.57</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O35" t="n">
         <v>2.45</v>
       </c>
-      <c r="M35" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.8</v>
-      </c>
       <c r="P35" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X35" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.33</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD35" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -678,7 +678,7 @@
         <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="P2" t="n">
         <v>2.35</v>
@@ -690,7 +690,7 @@
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>2.3</v>
@@ -708,16 +708,16 @@
         <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC2" t="n">
         <v>1.57</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="M12" t="n">
         <v>3.09</v>
       </c>
       <c r="N12" t="n">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>2.45</v>
@@ -1977,16 +1977,16 @@
         <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
         <v>1.11</v>
@@ -2004,7 +2004,7 @@
         <v>1.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AB12" t="n">
         <v>1.11</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>2.13</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.85</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V17" t="n">
         <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X17" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.3</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>2.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>4.85</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V18" t="n">
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X18" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.06</v>
+        <v>2.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X21" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.78</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.58</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
         <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="N24" t="n">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.43</v>
       </c>
       <c r="P24" t="n">
         <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.42</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X24" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AC24" t="n">
         <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="P25" t="n">
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="R25" t="n">
         <v>1.38</v>
@@ -3672,13 +3672,13 @@
         <v>1.33</v>
       </c>
       <c r="X25" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AA25" t="n">
         <v>3.75</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="O26" t="n">
-        <v>2.02</v>
+        <v>2.85</v>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
         <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Y26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2</v>
-      </c>
       <c r="AA26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.38</v>
+        <v>1.63</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>5.68</v>
       </c>
       <c r="O27" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T27" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD27" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.71</v>
+        <v>2.38</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="N28" t="n">
-        <v>2.61</v>
+        <v>2.79</v>
       </c>
       <c r="O28" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="V28" t="n">
         <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD28" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.81</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>5.35</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U29" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X29" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="N31" t="n">
-        <v>9.5</v>
+        <v>2.61</v>
       </c>
       <c r="O31" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="P31" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>3.28</v>
       </c>
       <c r="T31" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="U31" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="V31" t="n">
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.07</v>
+        <v>2.71</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.28</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.74</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>9.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.74</v>
+        <v>1.75</v>
       </c>
       <c r="P32" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="U32" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>3.55</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.74</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.1</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.35</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
-        <v>4.05</v>
+        <v>6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.3</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.25</v>
       </c>
-      <c r="S34" t="n">
+      <c r="X34" t="n">
         <v>3.8</v>
       </c>
-      <c r="T34" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U34" t="n">
+      <c r="Y34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.69</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AD34" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X2" t="n">
         <v>4.4</v>
@@ -711,10 +711,10 @@
         <v>1.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
         <v>1.48</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>2.87</v>
+        <v>3.09</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>5.6</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>7.6</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>2.99</v>
       </c>
       <c r="M18" t="n">
-        <v>4.3</v>
+        <v>2.41</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>2.93</v>
       </c>
       <c r="O18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N19" t="n">
-        <v>2.2</v>
+        <v>3.32</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="N20" t="n">
-        <v>2.67</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>3.31</v>
+        <v>4.3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z21" t="n">
         <v>2.55</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA21" t="n">
-        <v>3.98</v>
+        <v>2.3</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.22</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.08</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>1.27</v>
       </c>
       <c r="O22" t="n">
-        <v>2.65</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.63</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.71</v>
+        <v>1.06</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
         <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>4.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="X23" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.15</v>
+        <v>2.97</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.39</v>
+        <v>2.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.82</v>
+        <v>2.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.43</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.38</v>
+        <v>5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="25">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="O25" t="n">
         <v>3.74</v>
@@ -3675,10 +3675,10 @@
         <v>2.85</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
         <v>3.75</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="O26" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>5.68</v>
+        <v>3.87</v>
       </c>
       <c r="O27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.02</v>
       </c>
-      <c r="P27" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q27" t="n">
-        <v>5.4</v>
+        <v>4.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AA27" t="n">
-        <v>3</v>
+        <v>3.98</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="M28" t="n">
-        <v>3.62</v>
+        <v>3.37</v>
       </c>
       <c r="N28" t="n">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.97</v>
+        <v>3.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>2.85</v>
       </c>
       <c r="T28" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
         <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>1.29</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="P29" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.99</v>
       </c>
       <c r="M30" t="n">
-        <v>4.8</v>
+        <v>3.17</v>
       </c>
       <c r="N30" t="n">
-        <v>7.1</v>
+        <v>3.97</v>
       </c>
       <c r="O30" t="n">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.3</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.2</v>
-      </c>
       <c r="X30" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="M31" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>2.61</v>
+        <v>3.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3.15</v>
+        <v>2.43</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W31" t="n">
         <v>1.28</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.2</v>
-      </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.71</v>
+        <v>3.38</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="32">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>1.82</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.57</v>
       </c>
       <c r="N32" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="O32" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="P32" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.5</v>
+        <v>5.35</v>
       </c>
       <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.22</v>
       </c>
-      <c r="S32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AH32" t="n">
-        <v>3.55</v>
+        <v>2.28</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,49 +4668,49 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="N33" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O33" t="n">
         <v>2.75</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.74</v>
-      </c>
       <c r="P33" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="T33" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="U33" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V33" t="n">
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" t="n">
         <v>2.3</v>
@@ -4719,10 +4719,10 @@
         <v>1.63</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -5005,6 +5005,522 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M36" t="n">
+        <v>6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK39"/>
+  <dimension ref="A1:AK34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,16 +708,16 @@
         <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
         <v>1.57</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45965.41666666666</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="9">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.45833333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.47</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.09</v>
+        <v>2.55</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>4.22</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="V13" t="n">
         <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="X13" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.95</v>
+        <v>1.31</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.02</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="N17" t="n">
-        <v>7.6</v>
+        <v>2.52</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="M18" t="n">
-        <v>2.41</v>
+        <v>2.81</v>
       </c>
       <c r="N18" t="n">
-        <v>2.93</v>
+        <v>2.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="M19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.7</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M20" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3123,58 +3123,58 @@
         <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="P21" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.85</v>
+        <v>5.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>10</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>1.27</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>2.48</v>
       </c>
       <c r="P22" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.73</v>
+        <v>4.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="X22" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.63</v>
+        <v>3.38</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.04</v>
+        <v>1.83</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.06</v>
+        <v>1.87</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.25</v>
-      </c>
       <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.22</v>
       </c>
-      <c r="V23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="M24" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="P24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.25</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,28 +3636,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="O25" t="n">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="P25" t="n">
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="R25" t="n">
         <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
         <v>2.7</v>
@@ -3666,31 +3666,31 @@
         <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X25" t="n">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.77</v>
       </c>
-      <c r="AA25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>3.1</v>
@@ -3798,7 +3798,7 @@
         <v>1.07</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
         <v>2.72</v>
@@ -3816,7 +3816,7 @@
         <v>1.24</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
         <v>1.86</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.02</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>3.87</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.65</v>
       </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.98</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.78</v>
+        <v>3.55</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="M28" t="n">
-        <v>3.37</v>
+        <v>3.66</v>
       </c>
       <c r="N28" t="n">
-        <v>3.07</v>
+        <v>3.82</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S28" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Z28" t="n">
         <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.5</v>
+        <v>2.83</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="Q29" t="n">
         <v>5.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="U29" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X29" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="M30" t="n">
-        <v>3.17</v>
+        <v>3.85</v>
       </c>
       <c r="N30" t="n">
-        <v>3.97</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.63</v>
+        <v>1.97</v>
       </c>
       <c r="U30" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.3</v>
+        <v>1.96</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.33</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.92</v>
+        <v>2.49</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N31" t="n">
-        <v>3.73</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2.43</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="T31" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.38</v>
+        <v>2.71</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.70833333334</v>
       </c>
     </row>
     <row r="32">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3.57</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>4.2</v>
+        <v>2.46</v>
       </c>
       <c r="O32" t="n">
-        <v>2.14</v>
+        <v>2.74</v>
       </c>
       <c r="P32" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.35</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>3.98</v>
+        <v>6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.82</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.22</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="M33" t="n">
-        <v>3.62</v>
+        <v>5.14</v>
       </c>
       <c r="N33" t="n">
-        <v>2.79</v>
+        <v>8.23</v>
       </c>
       <c r="O33" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="P33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q33" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.61</v>
+        <v>3.72</v>
       </c>
       <c r="N34" t="n">
-        <v>3.81</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA34" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4876,651 +4876,6 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PSG</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Bayern München</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X35" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Union Saint-Gilloise</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6</v>
-      </c>
-      <c r="N36" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Liverpool</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X37" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Tottenham Hotspur</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>København</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N38" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
-        <v>45965.70833333334</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>45965</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Olympiakos Piraeus</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>PSV</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N39" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK34"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="P2" t="n">
         <v>2.35</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>4.4</v>
@@ -720,10 +720,10 @@
         <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>2.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45965.03125</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1439,17 +1439,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>1.78</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.17</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.39</v>
+        <v>6.56</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.8</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.2</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.55</v>
+        <v>3.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.54</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.91</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4.22</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="T13" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.11</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.31</v>
+        <v>2.47</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.04</v>
+        <v>4.04</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.15</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="S14" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="T14" t="n">
-        <v>3.48</v>
+        <v>4.4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.4</v>
+        <v>3.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.85</v>
+        <v>6.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.5</v>
+        <v>1.31</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>2.17</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>1.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.7</v>
+        <v>4.44</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>2.11</v>
       </c>
       <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X15" t="n">
         <v>2.15</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.8</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>3.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.43</v>
+        <v>6.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.6</v>
+        <v>1.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.62</v>
+        <v>2.53</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>10.5</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>5.5</v>
+        <v>2.85</v>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>2.76</v>
       </c>
       <c r="P16" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>5.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>2.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>4.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2</v>
+        <v>1.68</v>
       </c>
       <c r="X16" t="n">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>3.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.63</v>
+        <v>6.65</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>1.69</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,78 +2604,78 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.02</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.52</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>4.12</v>
+        <v>2.17</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>4.3</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.68</v>
+        <v>1.17</v>
       </c>
       <c r="X17" t="n">
-        <v>2.05</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.04</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.33</v>
+        <v>2.31</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="AC17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AD17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,58 +2733,58 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>10</v>
+      </c>
+      <c r="M18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O18" t="n">
+        <v>8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.3</v>
       </c>
-      <c r="M18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.3</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.5</v>
       </c>
-      <c r="X18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD18" t="n">
         <v>1.65</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>1.02</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="O19" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,11 +2929,11 @@
         </is>
       </c>
       <c r="AG19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AI19" t="n">
         <v>0</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>3.02</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="W20" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>3.09</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.84</v>
+        <v>1.51</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,19 +3058,19 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>2.18</v>
       </c>
       <c r="M21" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>2.02</v>
+        <v>2.71</v>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.4</v>
+        <v>4.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.89</v>
+        <v>4.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>7.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.66666666666</v>
       </c>
     </row>
     <row r="23">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.73</v>
       </c>
       <c r="O23" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
         <v>4.25</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.33</v>
+        <v>3.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,74 +3507,74 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="N24" t="n">
-        <v>3.28</v>
+        <v>3.97</v>
       </c>
       <c r="O24" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
         <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.28</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
         <v>1.71</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="X25" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC25" t="n">
         <v>1.94</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB25" t="n">
+      <c r="AD25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
         <v>1.26</v>
       </c>
-      <c r="AC25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="M27" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N27" t="n">
         <v>6</v>
       </c>
-      <c r="N27" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="O27" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="P27" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="V27" t="n">
         <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.55</v>
+        <v>2.38</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.93</v>
+        <v>2.68</v>
       </c>
       <c r="M28" t="n">
-        <v>3.66</v>
+        <v>3.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3.82</v>
+        <v>2.68</v>
       </c>
       <c r="O28" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
-        <v>3.8</v>
+        <v>2.68</v>
       </c>
       <c r="Y28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.1</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>3.87</v>
       </c>
       <c r="O29" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.68</v>
+        <v>3.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,62 +4281,62 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="M30" t="n">
-        <v>3.85</v>
+        <v>3.37</v>
       </c>
       <c r="N30" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.75</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4.3</v>
-      </c>
       <c r="T30" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.75</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X30" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="AD30" t="n">
         <v>1.96</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="31">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="M31" t="n">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="N31" t="n">
         <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P31" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="V31" t="n">
         <v>1.02</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.15</v>
+        <v>2.86</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,77 +4539,77 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O32" t="n">
         <v>2.5</v>
       </c>
-      <c r="M32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.74</v>
-      </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.36</v>
+        <v>2.45</v>
       </c>
       <c r="M33" t="n">
-        <v>5.14</v>
+        <v>3.58</v>
       </c>
       <c r="N33" t="n">
-        <v>8.23</v>
+        <v>2.61</v>
       </c>
       <c r="O33" t="n">
-        <v>1.91</v>
+        <v>3.05</v>
       </c>
       <c r="P33" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T33" t="n">
         <v>2.45</v>
       </c>
       <c r="U33" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>4.9</v>
+        <v>4.33</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AB33" t="n">
         <v>1.44</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>3</v>
+        <v>1.48</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,28 +4797,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="M34" t="n">
-        <v>3.72</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>9.5</v>
       </c>
       <c r="O34" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.97</v>
+        <v>7.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
         <v>2.36</v>
@@ -4830,52 +4830,568 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
         <v>1.14</v>
       </c>
-      <c r="X34" t="n">
+      <c r="X38" t="n">
         <v>5.6</v>
       </c>
-      <c r="Y34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA34" t="n">
+      <c r="Y38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z38" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
+      <c r="AA38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AH38" t="n">
         <v>1.57</v>
       </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" s="3" t="n">
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK38"/>
+  <dimension ref="A1:AK40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,34 +678,34 @@
         <v>4.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="P2" t="n">
         <v>2.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y2" t="n">
         <v>1.63</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45965.375</v>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45965.38541666666</v>
+        <v>45965.375</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45965.39583333334</v>
+        <v>45965.38541666666</v>
       </c>
     </row>
     <row r="7">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,16 +1417,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1439,17 +1439,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45965.41666666666</v>
+        <v>45965.39583333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1568,17 +1568,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,37 +1830,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.78</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.56</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>1.5</v>
@@ -1869,22 +1869,22 @@
         <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,86 +1959,86 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>10.06</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>1.35</v>
       </c>
       <c r="O12" t="n">
-        <v>2.63</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>2.19</v>
       </c>
       <c r="R12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z12" t="n">
         <v>1.42</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA12" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AK12" s="3" t="n">
-        <v>45965.54166666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P13" t="n">
         <v>2</v>
       </c>
-      <c r="P13" t="n">
-        <v>1.97</v>
-      </c>
       <c r="Q13" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
         <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="AB13" t="n">
         <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>4.04</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>2.08</v>
+        <v>3.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.21</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.9</v>
+        <v>3.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.04</v>
+        <v>1.28</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.59</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,19 +2284,19 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>2.63</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.44</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="X15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA15" t="n">
         <v>6.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.76</v>
+        <v>3.32</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.45</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
         <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="X16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.65</v>
+        <v>6.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,86 +2604,86 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>2.17</v>
+        <v>3.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.07</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>4.33</v>
       </c>
       <c r="U17" t="n">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="X17" t="n">
-        <v>4.8</v>
+        <v>2.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>3.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.31</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.27</v>
+        <v>6.7</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>8.9</v>
       </c>
       <c r="R18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.25</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.61</v>
-      </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.4</v>
+        <v>4.64</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,19 +2800,19 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.02</v>
+        <v>2.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,86 +2862,86 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.45</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.16</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.14</v>
+        <v>5.39</v>
       </c>
       <c r="R19" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.3</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.45</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>2.45</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,86 +2991,86 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.02</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>2.55</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.52</v>
+        <v>1.27</v>
       </c>
       <c r="O20" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>2.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.15</v>
       </c>
-      <c r="T20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="AA20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
         <v>1.15</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="21">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.18</v>
+        <v>3.02</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>2.71</v>
+        <v>4.12</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.68</v>
+        <v>3.54</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="S21" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="U21" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="W21" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="X21" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>3.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.3</v>
+        <v>6.55</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45965.625</v>
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,19 +3316,19 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45965.66666666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="23">
@@ -3337,12 +3337,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,86 +3378,86 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>3.73</v>
+        <v>2.2</v>
       </c>
       <c r="O23" t="n">
-        <v>2.57</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AD23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
         <v>1.35</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AD23" t="n">
+      <c r="AH23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.87</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
       <c r="AK23" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="24">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.99</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.97</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.66666666666</v>
       </c>
     </row>
     <row r="25">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.12</v>
+        <v>1.53</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.99</v>
       </c>
       <c r="N25" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.73</v>
+        <v>2.16</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.42</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA25" t="n">
         <v>3</v>
       </c>
-      <c r="Y25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.54</v>
+        <v>2.14</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.91</v>
+        <v>1.99</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>3.97</v>
       </c>
       <c r="O26" t="n">
-        <v>3.73</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.07</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Z26" t="n">
         <v>1.77</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.75</v>
+        <v>3.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI26" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.53</v>
+        <v>2.91</v>
       </c>
       <c r="M27" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>2.48</v>
       </c>
       <c r="O27" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.38</v>
       </c>
-      <c r="AC27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.68</v>
+        <v>1.92</v>
       </c>
       <c r="M28" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>2.68</v>
+        <v>3.73</v>
       </c>
       <c r="O28" t="n">
-        <v>3.15</v>
+        <v>2.59</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X28" t="n">
         <v>3.05</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.68</v>
-      </c>
       <c r="Y28" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="M29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O29" t="n">
         <v>3.15</v>
       </c>
-      <c r="N29" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
         <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W29" t="n">
         <v>1.41</v>
       </c>
       <c r="X29" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="Y29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4290,25 +4290,25 @@
         <v>3.07</v>
       </c>
       <c r="O30" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="P30" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
         <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V30" t="n">
         <v>1.02</v>
@@ -4317,7 +4317,7 @@
         <v>1.27</v>
       </c>
       <c r="X30" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="Y30" t="n">
         <v>1.79</v>
@@ -4329,7 +4329,7 @@
         <v>3.45</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC30" t="n">
         <v>1.75</v>
@@ -4354,10 +4354,10 @@
         <v>1.57</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="M31" t="n">
-        <v>3.74</v>
+        <v>3.19</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>3.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.74</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="X31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.86</v>
+        <v>1.55</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>1.21</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.95</v>
+        <v>1.86</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,19 +4477,19 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,86 +4539,86 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="M32" t="n">
-        <v>3.98</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.88</v>
+        <v>3.87</v>
       </c>
       <c r="O32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>2.5</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="33">
@@ -4677,7 +4677,7 @@
         <v>2.61</v>
       </c>
       <c r="O33" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P33" t="n">
         <v>2.3</v>
@@ -4701,7 +4701,7 @@
         <v>1.02</v>
       </c>
       <c r="W33" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
         <v>4.33</v>
@@ -4713,7 +4713,7 @@
         <v>2</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AB33" t="n">
         <v>1.44</v>
@@ -4741,10 +4741,10 @@
         <v>1.48</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,28 +4797,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="N34" t="n">
-        <v>9.5</v>
+        <v>2.79</v>
       </c>
       <c r="O34" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="P34" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.5</v>
+        <v>2.97</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
         <v>2.36</v>
@@ -4830,28 +4830,28 @@
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.93</v>
+        <v>1.43</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AH34" t="n">
-        <v>3.45</v>
+        <v>1.57</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.82</v>
+        <v>2.28</v>
       </c>
       <c r="M35" t="n">
-        <v>3.57</v>
+        <v>3.74</v>
       </c>
       <c r="N35" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="O35" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.41</v>
+        <v>3.05</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.46</v>
+        <v>1.74</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="X35" t="n">
-        <v>4.08</v>
+        <v>6</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.15</v>
+        <v>2.86</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4996,13 +4996,13 @@
         <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.26</v>
+        <v>1.48</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="M36" t="n">
-        <v>3.61</v>
+        <v>6</v>
       </c>
       <c r="N36" t="n">
-        <v>3.81</v>
+        <v>9.5</v>
       </c>
       <c r="O36" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>7.3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="S36" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U36" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>3.8</v>
+        <v>6.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.98</v>
+        <v>2.57</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.84</v>
+        <v>2.07</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AI36" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="M37" t="n">
-        <v>4.8</v>
+        <v>3.61</v>
       </c>
       <c r="N37" t="n">
-        <v>7.1</v>
+        <v>3.81</v>
       </c>
       <c r="O37" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="P37" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.5</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5277,121 +5277,379 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK38" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>Europe UEFA Champions League</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>FK Bodo - Glimt</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O38" t="n">
+      <c r="L39" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P39" t="n">
         <v>2.75</v>
       </c>
-      <c r="P38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="Q39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V39" t="n">
         <v>1.01</v>
       </c>
-      <c r="W38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="3" t="n">
+      <c r="W39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AK39" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>København</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK40" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -672,13 +672,13 @@
         <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="P2" t="n">
         <v>2.35</v>
@@ -690,16 +690,16 @@
         <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
         <v>1.18</v>
@@ -708,19 +708,19 @@
         <v>4.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AD2" t="n">
         <v>2.1</v>
@@ -739,7 +739,7 @@
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AI2" t="n">
         <v>1.5</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45965.33333333334</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="N4" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
         <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45965.375</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45965.375</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45965.38541666666</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,23 +1314,23 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.25</v>
+        <v>2.1</v>
       </c>
       <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3.6</v>
       </c>
-      <c r="N7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45965.39583333334</v>
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="N10" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45965.4375</v>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45965.4375</v>
@@ -1959,37 +1959,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>10.06</v>
+        <v>13</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="N12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>8.550000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="T12" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="U12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
         <v>1.47</v>
@@ -1998,22 +1998,22 @@
         <v>2.47</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
         <v>1.03</v>
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -2106,43 +2106,43 @@
         <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.55</v>
+        <v>4.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC13" t="n">
         <v>2.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" t="n">
         <v>1.61</v>
@@ -2217,34 +2217,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>13.2</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>151</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
         <v>1.06</v>
@@ -2253,19 +2253,19 @@
         <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC14" t="n">
         <v>1.75</v>
@@ -2287,7 +2287,7 @@
         <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AI14" t="n">
         <v>1.8</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,58 +2346,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>7.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.63</v>
+        <v>2.03</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>8.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.21</v>
+        <v>2.41</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.15</v>
+        <v>4.64</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AD15" t="n">
         <v>1.44</v>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="M16" t="n">
         <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="O16" t="n">
         <v>3.32</v>
@@ -2490,7 +2490,7 @@
         <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="R16" t="n">
         <v>1.68</v>
@@ -2508,16 +2508,16 @@
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA16" t="n">
         <v>6.05</v>
@@ -2526,10 +2526,10 @@
         <v>1.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="n">
         <v>1.53</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,58 +2604,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>4.55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.98</v>
+        <v>2.63</v>
       </c>
       <c r="P17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.67</v>
-      </c>
       <c r="S17" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="T17" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
         <v>1.67</v>
       </c>
       <c r="X17" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.75</v>
+        <v>6.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AD17" t="n">
         <v>1.46</v>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>3.01</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="N18" t="n">
-        <v>6.7</v>
+        <v>2.78</v>
       </c>
       <c r="O18" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Y18" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="Z18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA18" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
         <v>1.03</v>
@@ -2898,41 +2898,41 @@
         <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="Y19" t="n">
         <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AD19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI19" t="n">
         <v>1.48</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>11</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O20" t="n">
         <v>10</v>
       </c>
-      <c r="M20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O20" t="n">
-        <v>8</v>
-      </c>
       <c r="P20" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z20" t="n">
         <v>2.2</v>
       </c>
-      <c r="U20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AA20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AI20" t="n">
         <v>3.75</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.02</v>
+        <v>3.4</v>
       </c>
       <c r="M21" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>4.12</v>
+        <v>4.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="U21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.09</v>
+        <v>2.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.55</v>
+        <v>5.06</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45965.625</v>
@@ -3249,28 +3249,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.77</v>
+        <v>4.92</v>
       </c>
       <c r="R22" t="n">
         <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
         <v>3.35</v>
@@ -3285,25 +3285,25 @@
         <v>1.37</v>
       </c>
       <c r="X22" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AA22" t="n">
         <v>4.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AI22" t="n">
         <v>1.72</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>4.12</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.9</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="S23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.3</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45965.625</v>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3558,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45965.66666666666</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.53</v>
+        <v>2.19</v>
       </c>
       <c r="M25" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>2.16</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="X25" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.17</v>
+        <v>3.54</v>
       </c>
       <c r="N26" t="n">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="O26" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.8</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.08</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.57</v>
+        <v>3.9</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.23</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.91</v>
+        <v>1.67</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.48</v>
+        <v>4.69</v>
       </c>
       <c r="O27" t="n">
-        <v>3.5</v>
+        <v>2.22</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>2.55</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.75</v>
+        <v>2.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,80 +4023,80 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="M28" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.73</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.35</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W28" t="n">
+      <c r="X28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.33</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z28" t="n">
+      <c r="AH28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.72</v>
       </c>
       <c r="AJ28" t="n">
         <v>2.4</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.68</v>
+        <v>2.97</v>
       </c>
       <c r="M29" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="O29" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X29" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>3.37</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>3.07</v>
+        <v>2.85</v>
       </c>
       <c r="O30" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>2.14</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="M31" t="n">
-        <v>3.19</v>
+        <v>3.34</v>
       </c>
       <c r="N31" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q31" t="n">
         <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T31" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U31" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X31" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,13 +4477,13 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AJ31" t="n">
         <v>2.4</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
-        <v>3.87</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.7</v>
       </c>
-      <c r="T32" t="n">
-        <v>3</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.36</v>
       </c>
-      <c r="X32" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="O33" t="n">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="T33" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="U33" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>4.33</v>
+        <v>5.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
-        <v>2</v>
+        <v>2.72</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AC33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI33" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M34" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="O34" t="n">
         <v>2.75</v>
@@ -4812,19 +4812,19 @@
         <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="R34" t="n">
         <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T34" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="U34" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
@@ -4833,25 +4833,25 @@
         <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,22 +4926,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="M35" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="N35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P35" t="n">
         <v>2.75</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.6</v>
-      </c>
       <c r="Q35" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="R35" t="n">
         <v>1.2</v>
@@ -4953,34 +4953,34 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>9.5</v>
+        <v>5.06</v>
       </c>
       <c r="O36" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="P36" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>7.3</v>
+        <v>5.48</v>
       </c>
       <c r="R36" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="U36" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X36" t="n">
-        <v>6.25</v>
+        <v>3.92</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.57</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.07</v>
+        <v>2.72</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>3.45</v>
+        <v>2.26</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.81</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="P37" t="n">
         <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U37" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="AA37" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.82</v>
+        <v>1.27</v>
       </c>
       <c r="M38" t="n">
-        <v>3.57</v>
+        <v>6.5</v>
       </c>
       <c r="N38" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="O38" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="P38" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.41</v>
+        <v>6.38</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="T38" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="V38" t="n">
         <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X38" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.72</v>
+        <v>2.28</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="M39" t="n">
-        <v>3.98</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.88</v>
+        <v>3.95</v>
       </c>
       <c r="O39" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.5</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.97</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X39" t="n">
-        <v>7</v>
+        <v>3.74</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.21</v>
+        <v>1.95</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.83</v>
+        <v>2.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5571,25 +5571,25 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="M40" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="N40" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="P40" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="R40" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
         <v>3.3</v>
@@ -5598,34 +5598,34 @@
         <v>2.45</v>
       </c>
       <c r="U40" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X40" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC40" t="n">
         <v>1.91</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="AI40" t="n">
         <v>1.33</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="N4" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.64</v>
+        <v>4.43</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
         <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X4" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45965.375</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
         <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AC5" t="n">
         <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45965.375</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="M7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="N7" t="n">
+      <c r="T7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA7" t="n">
         <v>3.3</v>
       </c>
-      <c r="O7" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45965.39583333334</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.8</v>
+        <v>2.13</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.64</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.57</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45965.39583333334</v>
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="R10" t="n">
         <v>1.73</v>
@@ -1734,16 +1734,16 @@
         <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AA10" t="n">
         <v>7</v>
@@ -1752,10 +1752,10 @@
         <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N11" t="n">
         <v>2.7</v>
       </c>
       <c r="O11" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="R11" t="n">
         <v>1.53</v>
@@ -1863,16 +1863,16 @@
         <v>1.05</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AA11" t="n">
         <v>5.1</v>
@@ -1881,10 +1881,10 @@
         <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1962,25 +1962,25 @@
         <v>13</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
         <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>12.5</v>
+        <v>12.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
         <v>3.58</v>
@@ -1989,7 +1989,7 @@
         <v>1.21</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
         <v>1.47</v>
@@ -2010,7 +2010,7 @@
         <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
         <v>1.27</v>
@@ -2029,7 +2029,7 @@
         <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>4.5</v>
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
@@ -2106,43 +2106,43 @@
         <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="V13" t="n">
         <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AA13" t="n">
         <v>4.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AI13" t="n">
         <v>1.61</v>
@@ -2217,28 +2217,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>13.2</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>151</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.65</v>
+        <v>3.37</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="T14" t="n">
         <v>2.85</v>
@@ -2256,19 +2256,19 @@
         <v>3.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="AB14" t="n">
         <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="n">
         <v>1.95</v>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AI14" t="n">
         <v>1.8</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.44</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N15" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.33</v>
+        <v>6.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.32</v>
+        <v>2.07</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.44</v>
+        <v>7.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.11</v>
+        <v>2.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.05</v>
+        <v>4.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.32</v>
+        <v>2.81</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="M17" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4.55</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>2.63</v>
+        <v>3.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>4.44</v>
       </c>
       <c r="R17" t="n">
         <v>1.68</v>
       </c>
       <c r="S17" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="T17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W17" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="X17" t="n">
         <v>2.15</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="AB17" t="n">
         <v>1.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2733,19 +2733,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="P18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
         <v>3.7</v>
@@ -2754,40 +2754,40 @@
         <v>1.67</v>
       </c>
       <c r="S18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="V18" t="n">
         <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="Z18" t="n">
         <v>1.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AB18" t="n">
         <v>1.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH18" t="n">
         <v>1.36</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="O21" t="n">
-        <v>4.38</v>
+        <v>4.19</v>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="T21" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="X21" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.5</v>
+        <v>3.09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.06</v>
+        <v>6.6</v>
       </c>
       <c r="AB21" t="n">
         <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45965.625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>2.66</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45965.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="M23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.75</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Y23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45965.625</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
         <v>2.2</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.19</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>4.69</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.22</v>
       </c>
       <c r="P25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH25" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AI25" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y26" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.29</v>
-      </c>
       <c r="Z26" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q27" t="n">
         <v>4</v>
       </c>
-      <c r="N27" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>2.6</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="P28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="T28" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
         <v>3.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.81</v>
+        <v>3.64</v>
       </c>
       <c r="AB28" t="n">
         <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,31 +4152,31 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.97</v>
+        <v>1.99</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="N29" t="n">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T29" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U29" t="n">
         <v>1.34</v>
@@ -4185,28 +4185,28 @@
         <v>1.07</v>
       </c>
       <c r="W29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X29" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.91</v>
+        <v>3.44</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O31" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="P31" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q31" t="n">
         <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V31" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W31" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X31" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.08</v>
       </c>
-      <c r="Z31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.3</v>
+        <v>2.97</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="O32" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="P32" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.64</v>
+        <v>3.91</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.47</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.7</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH33" t="n">
         <v>3.75</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X33" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AI33" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="M34" t="n">
         <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="O34" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U34" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.63</v>
+        <v>3.21</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>2.37</v>
-      </c>
-      <c r="M35" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X35" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.9</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.64</v>
+        <v>2.41</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>5.06</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="P36" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.48</v>
+        <v>3.18</v>
       </c>
       <c r="R36" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T36" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X36" t="n">
-        <v>3.92</v>
+        <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="Z36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>2</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="M38" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>5.06</v>
       </c>
       <c r="O38" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="P38" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.38</v>
+        <v>5.48</v>
       </c>
       <c r="R38" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="U38" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X38" t="n">
-        <v>5</v>
+        <v>3.92</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AH38" t="n">
-        <v>3.75</v>
+        <v>2.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="N39" t="n">
-        <v>3.95</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>2.52</v>
+        <v>1.81</v>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
       <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.33</v>
       </c>
-      <c r="S39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AJ39" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.25</v>
+        <v>2.37</v>
       </c>
       <c r="M40" t="n">
-        <v>5.3</v>
+        <v>3.95</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="O40" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="Q40" t="n">
-        <v>7.5</v>
+        <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.29</v>
+        <v>3</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.55</v>
+        <v>1.94</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.79</v>
+        <v>3.1</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AH40" t="n">
-        <v>3.36</v>
+        <v>1.54</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45965.70833333334</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O2" t="n">
         <v>2.05</v>
@@ -687,7 +687,7 @@
         <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
         <v>3.4</v>
@@ -696,7 +696,7 @@
         <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
@@ -711,16 +711,16 @@
         <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AD2" t="n">
         <v>2.1</v>
@@ -739,7 +739,7 @@
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AI2" t="n">
         <v>1.5</v>
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.26</v>
+        <v>2.33</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.75</v>
+        <v>5.53</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AB3" t="n">
         <v>1.24</v>
@@ -852,7 +852,7 @@
         <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AI3" t="n">
         <v>1.57</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
         <v>3.1</v>
@@ -966,10 +966,10 @@
         <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
         <v>4.95</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
         <v>3.35</v>
@@ -1077,7 +1077,7 @@
         <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
@@ -1092,13 +1092,13 @@
         <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="Y5" t="n">
         <v>2.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AA5" t="n">
         <v>5.45</v>
@@ -1110,7 +1110,7 @@
         <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="P6" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.2</v>
+        <v>6.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="T6" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="Y6" t="n">
         <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AI6" t="n">
         <v>1.45</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.7</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O10" t="n">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.86</v>
+        <v>3.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="U10" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.53</v>
+        <v>2.08</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45965.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.38</v>
+        <v>3.65</v>
       </c>
       <c r="P11" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.52</v>
+        <v>3.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45965.4375</v>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O12" t="n">
-        <v>12.25</v>
+        <v>5.8</v>
       </c>
       <c r="P12" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
         <v>1.65</v>
@@ -1983,25 +1983,25 @@
         <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="Y12" t="n">
         <v>2.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA12" t="n">
         <v>4.8</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" t="n">
         <v>4.5</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>6.7</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.07</v>
+        <v>3.36</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.1</v>
+        <v>4.44</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.44</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>3.36</v>
+        <v>3.92</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.44</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="X17" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.05</v>
+        <v>6.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,13 +2674,13 @@
         <v>1.44</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>6.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.92</v>
+        <v>2.07</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="R18" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>4.25</v>
+        <v>3.38</v>
       </c>
       <c r="U18" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.21</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.6</v>
+        <v>4.72</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI18" t="n">
         <v>1.44</v>
       </c>
-      <c r="AH18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>11</v>
       </c>
       <c r="M19" t="n">
-        <v>4.36</v>
+        <v>5.75</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>1.26</v>
       </c>
       <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.1</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.48</v>
+        <v>3.75</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.81</v>
+        <v>1.28</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45965.61458333334</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>11</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>5.75</v>
+        <v>4.36</v>
       </c>
       <c r="N20" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>10</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.68</v>
+        <v>5.39</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>1.64</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,13 +3061,13 @@
         <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.06</v>
+        <v>2.42</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>2.81</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45965.61458333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.02</v>
+        <v>2.18</v>
       </c>
       <c r="M21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.55</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AI21" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45965.625</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="M22" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>4.19</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="T22" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
         <v>1.21</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="X22" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.49</v>
+        <v>3.09</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.06</v>
+        <v>6.6</v>
       </c>
       <c r="AB22" t="n">
         <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.32</v>
       </c>
-      <c r="AH22" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AI22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45965.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.02</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
         <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="T23" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.85</v>
+        <v>2.49</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.2</v>
+        <v>5.06</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45965.625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>4.69</v>
+        <v>3.87</v>
       </c>
       <c r="O25" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="P25" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.75</v>
+        <v>4.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>3.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.04</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="X25" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.83</v>
+        <v>3.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.19</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
         <v>2.69</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="U26" t="n">
         <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X26" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.28</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.98</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.39</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U27" t="n">
         <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="X27" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4023,58 +4023,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="O28" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="P28" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="Q28" t="n">
         <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
         <v>3.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD28" t="n">
         <v>2</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI28" t="n">
         <v>1.84</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>3.34</v>
+        <v>3.99</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>2.6</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>1.99</v>
       </c>
       <c r="M30" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.9</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.28</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X30" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AJ30" t="n">
         <v>2.2</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y31" t="n">
         <v>2</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="Z31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA31" t="n">
         <v>3.8</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4539,58 +4539,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="O32" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="U32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.91</v>
+        <v>3.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AD32" t="n">
         <v>1.91</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI32" t="n">
         <v>2.2</v>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="M33" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="N33" t="n">
         <v>10</v>
@@ -4680,10 +4680,10 @@
         <v>1.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.38</v>
+        <v>7.8</v>
       </c>
       <c r="R33" t="n">
         <v>1.25</v>
@@ -4707,22 +4707,22 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z33" t="n">
         <v>2.62</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AB33" t="n">
         <v>1.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AI33" t="n">
         <v>1.3</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.47</v>
+        <v>1.82</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.57</v>
       </c>
       <c r="N34" t="n">
-        <v>2.33</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2.76</v>
+        <v>2.15</v>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="R34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
         <v>1.22</v>
       </c>
-      <c r="S34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.08</v>
-      </c>
       <c r="X34" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.72</v>
+        <v>2.15</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.21</v>
+        <v>1.97</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="O35" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S35" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X35" t="n">
-        <v>3.74</v>
+        <v>5.55</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="R36" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="U36" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X36" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.6</v>
+        <v>2.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.63</v>
+        <v>3.19</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M37" t="n">
         <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
         <v>3.15</v>
@@ -5223,7 +5223,7 @@
         <v>4.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Z37" t="n">
         <v>2.23</v>
@@ -5232,13 +5232,13 @@
         <v>2.61</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" t="n">
         <v>1.9</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,34 +5313,34 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>5.35</v>
       </c>
       <c r="N38" t="n">
-        <v>5.06</v>
+        <v>8</v>
       </c>
       <c r="O38" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="P38" t="n">
         <v>2.45</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.48</v>
+        <v>7.5</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
         <v>3.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
@@ -5349,25 +5349,25 @@
         <v>1.18</v>
       </c>
       <c r="X38" t="n">
-        <v>3.92</v>
+        <v>4.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AD38" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5383,13 +5383,13 @@
         <v>1.17</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.26</v>
+        <v>3.42</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.25</v>
+        <v>2.37</v>
       </c>
       <c r="M39" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="P39" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S39" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.79</v>
+        <v>3.1</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>3.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>2.37</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X40" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.9</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45965.70833333334</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -652,94 +652,94 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>6.15</v>
       </c>
       <c r="O2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD2" t="n">
         <v>2.05</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '21', '41', '86']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '45+5']</t>
         </is>
       </c>
       <c r="AG2" t="n">
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AI2" t="n">
         <v>1.5</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AA3" t="n">
         <v>4.5</v>
       </c>
-      <c r="O3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="AB3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AI3" t="n">
         <v>1.57</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.2</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.18</v>
-      </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
         <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="X4" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.95</v>
+        <v>5.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45965.375</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.62</v>
+        <v>2.22</v>
       </c>
       <c r="M5" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>2.64</v>
+        <v>3.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.62</v>
+        <v>4.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45965.375</v>
@@ -1185,37 +1185,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="N6" t="n">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="O6" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.84</v>
+        <v>6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
         <v>1.16</v>
@@ -1224,7 +1224,7 @@
         <v>4.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
         <v>2.08</v>
@@ -1236,10 +1236,10 @@
         <v>1.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="AI6" t="n">
         <v>1.45</v>
@@ -1323,34 +1323,34 @@
         <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>5.28</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y7" t="n">
         <v>1.85</v>
@@ -1359,16 +1359,16 @@
         <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AI7" t="n">
         <v>2.62</v>
@@ -1452,19 +1452,19 @@
         <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.76</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
         <v>3</v>
@@ -1482,7 +1482,7 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
         <v>1.65</v>
@@ -1494,10 +1494,10 @@
         <v>1.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
         <v>1.83</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.38</v>
+        <v>3.66</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.52</v>
+        <v>3.86</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="S10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45965.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N11" t="n">
         <v>2.7</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O11" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="T11" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="U11" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AA11" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45965.4375</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.5</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.68</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.49</v>
+        <v>2.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>3.25</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45965.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>2.14</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="U13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.21</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AH13" t="n">
         <v>1.1</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AI13" t="n">
-        <v>1.61</v>
+        <v>4.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45965.5</v>
@@ -2226,25 +2226,25 @@
         <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
         <v>1.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
         <v>1.06</v>
@@ -2253,7 +2253,7 @@
         <v>1.28</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Y14" t="n">
         <v>1.85</v>
@@ -2262,16 +2262,16 @@
         <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="AB14" t="n">
         <v>1.25</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AI14" t="n">
         <v>1.8</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,43 +2346,43 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="M15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N15" t="n">
         <v>2.85</v>
       </c>
-      <c r="N15" t="n">
-        <v>4.9</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="P15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="T15" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Y15" t="n">
         <v>3.21</v>
@@ -2391,13 +2391,13 @@
         <v>1.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.15</v>
+        <v>6.4</v>
       </c>
       <c r="AB15" t="n">
         <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
         <v>1.5</v>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>6.7</v>
       </c>
       <c r="O16" t="n">
-        <v>3.36</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.44</v>
+        <v>7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="U16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.2</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,43 +2604,43 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.92</v>
+        <v>2.63</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.7</v>
+        <v>4.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.08</v>
       </c>
       <c r="Y17" t="n">
         <v>3.21</v>
@@ -2649,16 +2649,16 @@
         <v>1.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.6</v>
+        <v>6.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N18" t="n">
-        <v>6.7</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.5</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.5</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2862,25 +2862,25 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="N19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
         <v>3.3</v>
@@ -2889,7 +2889,7 @@
         <v>2.49</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
@@ -2898,25 +2898,25 @@
         <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2991,77 +2991,77 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.39</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S20" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
         <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="Y20" t="n">
         <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.42</v>
       </c>
       <c r="AI20" t="n">
         <v>1.48</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="O21" t="n">
-        <v>2.63</v>
+        <v>3.69</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.02</v>
+        <v>2.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="S21" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="T21" t="n">
-        <v>3.28</v>
+        <v>3.58</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W21" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45965.625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.02</v>
+        <v>2.18</v>
       </c>
       <c r="M22" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>4.19</v>
+        <v>2.47</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V22" t="n">
         <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="X22" t="n">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.09</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.6</v>
+        <v>4.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.68</v>
+        <v>2.01</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45965.625</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,62 +3378,62 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q23" t="n">
         <v>3.4</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.9</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="S23" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="U23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.5</v>
       </c>
-      <c r="X23" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE23" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45965.625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.87</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
-        <v>2.49</v>
+        <v>2.92</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.16</v>
+        <v>3.39</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="X25" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3706,13 +3706,13 @@
         <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,80 +3894,80 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.68</v>
+        <v>1.99</v>
       </c>
       <c r="M27" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X27" t="n">
         <v>3.08</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="Y27" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AI27" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.9</v>
       </c>
       <c r="AJ27" t="n">
         <v>2.2</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.23</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>3.37</v>
+        <v>3.99</v>
       </c>
       <c r="N28" t="n">
-        <v>3.07</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="P28" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.36</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AC28" t="n">
         <v>1.79</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.57</v>
       </c>
-      <c r="AI28" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>2.91</v>
       </c>
       <c r="M29" t="n">
-        <v>3.99</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>2.48</v>
       </c>
       <c r="O29" t="n">
-        <v>2.28</v>
+        <v>3.29</v>
       </c>
       <c r="P29" t="n">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.7</v>
+        <v>2.87</v>
       </c>
       <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.33</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="X29" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.25</v>
       </c>
-      <c r="X29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI29" t="n">
         <v>2.2</v>
       </c>
-      <c r="AI29" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,28 +4281,28 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="M30" t="n">
-        <v>3.17</v>
+        <v>3.37</v>
       </c>
       <c r="N30" t="n">
-        <v>3.97</v>
+        <v>3.07</v>
       </c>
       <c r="O30" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="P30" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.43</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
         <v>2.9</v>
@@ -4311,31 +4311,31 @@
         <v>1.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X30" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AA30" t="n">
         <v>3.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.91</v>
+        <v>2.02</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.48</v>
+        <v>3.87</v>
       </c>
       <c r="O32" t="n">
-        <v>3.29</v>
+        <v>2.49</v>
       </c>
       <c r="P32" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.87</v>
+        <v>4.16</v>
       </c>
       <c r="R32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.85</v>
+        <v>3.38</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X32" t="n">
-        <v>3.19</v>
+        <v>2.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,13 +4609,13 @@
         <v>1.36</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="M33" t="n">
-        <v>6.2</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>3.81</v>
       </c>
       <c r="O33" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.8</v>
+        <v>3.9</v>
       </c>
       <c r="R33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.25</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X33" t="n">
-        <v>5</v>
+        <v>3.74</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.62</v>
+        <v>1.98</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AJ33" t="n">
-        <v>3.4</v>
+        <v>2.37</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="M34" t="n">
-        <v>3.57</v>
+        <v>4.8</v>
       </c>
       <c r="N34" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X34" t="n">
         <v>4.2</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4</v>
-      </c>
       <c r="Y34" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="N35" t="n">
-        <v>2.95</v>
+        <v>2.61</v>
       </c>
       <c r="O35" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P35" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="U35" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X35" t="n">
-        <v>5.55</v>
+        <v>4.33</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="O36" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="U36" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X36" t="n">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5128,10 +5128,10 @@
         <v>1.53</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.47</v>
+        <v>1.26</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="O37" t="n">
-        <v>3.15</v>
+        <v>1.66</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.05</v>
+        <v>7.8</v>
       </c>
       <c r="R37" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="S37" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T37" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
         <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.23</v>
+        <v>2.57</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.61</v>
+        <v>2.07</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.46</v>
+        <v>1.91</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AI37" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AJ37" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="M38" t="n">
-        <v>5.35</v>
+        <v>3.62</v>
       </c>
       <c r="N38" t="n">
-        <v>8</v>
+        <v>2.79</v>
       </c>
       <c r="O38" t="n">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X38" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z38" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC38" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>3.42</v>
+        <v>1.62</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AJ38" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="N39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P39" t="n">
         <v>2.6</v>
       </c>
-      <c r="O39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R39" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U39" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>6.25</v>
+        <v>5.85</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="N40" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O40" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="R40" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T40" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="U40" t="n">
         <v>1.47</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X40" t="n">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="AB40" t="n">
         <v>1.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45965.70833333334</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="M3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.25</v>
       </c>
-      <c r="N3" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.44</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.37</v>
-      </c>
       <c r="X3" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AI3" t="n">
         <v>1.57</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.62</v>
+        <v>4.43</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
         <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45965.375</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.43</v>
+        <v>3.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.95</v>
+        <v>5.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45965.375</v>
@@ -1185,31 +1185,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>6.35</v>
+        <v>6.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
         <v>1.45</v>
@@ -1218,16 +1218,16 @@
         <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AA6" t="n">
         <v>2.62</v>
@@ -1239,7 +1239,7 @@
         <v>1.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="AI6" t="n">
         <v>1.45</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.7</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O10" t="n">
-        <v>3.66</v>
+        <v>3.22</v>
       </c>
       <c r="P10" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.86</v>
+        <v>4.25</v>
       </c>
       <c r="R10" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="U10" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.53</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45965.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.22</v>
+        <v>3.66</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="T11" t="n">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45965.4375</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>12</v>
       </c>
       <c r="M12" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>1.35</v>
       </c>
       <c r="O12" t="n">
-        <v>2.28</v>
+        <v>5.8</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.45</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="T12" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.51</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.61</v>
+        <v>4.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45965.5</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="N13" t="n">
-        <v>1.35</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>5.8</v>
+        <v>2.28</v>
       </c>
       <c r="P13" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>6.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.5</v>
+        <v>1.61</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.3</v>
+        <v>3.25</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45965.5</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,43 +2346,43 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="M15" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>4.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X15" t="n">
         <v>2.05</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.08</v>
       </c>
       <c r="Y15" t="n">
         <v>3.21</v>
@@ -2391,16 +2391,16 @@
         <v>1.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.4</v>
+        <v>6.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="M16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3.5</v>
       </c>
-      <c r="N16" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.05</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.55</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.83</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="U17" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="V17" t="n">
         <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="X17" t="n">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.21</v>
+        <v>2.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.15</v>
+        <v>4.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2862,19 +2862,19 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>12</v>
+      </c>
+      <c r="M19" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O19" t="n">
         <v>10</v>
       </c>
-      <c r="M19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O19" t="n">
-        <v>9</v>
-      </c>
       <c r="P19" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q19" t="n">
         <v>1.62</v>
@@ -2886,31 +2886,31 @@
         <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
         <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
         <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AC19" t="n">
         <v>2.2</v>
@@ -2991,52 +2991,52 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="N20" t="n">
         <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="Q20" t="n">
         <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
         <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X20" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="Y20" t="n">
         <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AB20" t="n">
         <v>1.63</v>
@@ -3045,7 +3045,7 @@
         <v>1.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AI20" t="n">
         <v>1.48</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>3.69</v>
+        <v>2.47</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>3.58</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="X21" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45965.625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="O22" t="n">
-        <v>2.47</v>
+        <v>3.69</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="V22" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W22" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45965.625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.68</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.39</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="T25" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
         <v>1.08</v>
       </c>
       <c r="W25" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="X25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AA25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.19</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>4.08</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
-        <v>3.02</v>
+        <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,13 +3835,13 @@
         <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.99</v>
+        <v>2.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>3.97</v>
+        <v>2.87</v>
       </c>
       <c r="O27" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
         <v>2.03</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.43</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>3.27</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="X27" t="n">
-        <v>3.08</v>
+        <v>2.54</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,13 +3961,13 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AJ27" t="n">
         <v>2.2</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.53</v>
+        <v>3.03</v>
       </c>
       <c r="M28" t="n">
-        <v>3.99</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
-        <v>2.28</v>
+        <v>3.83</v>
       </c>
       <c r="P28" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.33</v>
       </c>
-      <c r="S28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X28" t="n">
-        <v>3.9</v>
+        <v>2.89</v>
       </c>
       <c r="Y28" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI28" t="n">
         <v>2.2</v>
       </c>
-      <c r="AI28" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,31 +4152,31 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.91</v>
+        <v>2.13</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="N29" t="n">
-        <v>2.48</v>
+        <v>2.96</v>
       </c>
       <c r="O29" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="P29" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T29" t="n">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="U29" t="n">
         <v>1.35</v>
@@ -4188,22 +4188,22 @@
         <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
         <v>1.91</v>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="M30" t="n">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>3.93</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="T30" t="n">
         <v>2.9</v>
       </c>
       <c r="U30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.36</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W30" t="n">
+      <c r="X30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.29</v>
       </c>
-      <c r="X30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AI30" t="n">
         <v>1.84</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>3.73</v>
+        <v>4.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="T31" t="n">
         <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X31" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
         <v>1.91</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="O32" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="P32" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="T32" t="n">
-        <v>3.38</v>
+        <v>2.94</v>
       </c>
       <c r="U32" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X32" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>3.61</v>
+        <v>6.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.81</v>
+        <v>12</v>
       </c>
       <c r="O33" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="P33" t="n">
-        <v>2.21</v>
+        <v>2.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>3.74</v>
+        <v>4.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.72</v>
+        <v>1.97</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>7.1</v>
+        <v>2.79</v>
       </c>
       <c r="O34" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.4</v>
+        <v>3.15</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="V34" t="n">
         <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AC34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>3.4</v>
+        <v>1.94</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>2.61</v>
+        <v>3.8</v>
       </c>
       <c r="O35" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
         <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T35" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W35" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.52</v>
+        <v>2.1</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5055,31 +5055,31 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="N36" t="n">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="O36" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P36" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T36" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
         <v>1.75</v>
@@ -5088,28 +5088,28 @@
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI36" t="n">
         <v>1.83</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>9.5</v>
+        <v>5.54</v>
       </c>
       <c r="O37" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="Q37" t="n">
-        <v>7.8</v>
+        <v>5.35</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="T37" t="n">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="U37" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC37" t="n">
         <v>1.7</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X37" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>3.84</v>
+        <v>2.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="M38" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="O38" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
         <v>3.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="U38" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="V38" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AI38" t="n">
         <v>1.87</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.28</v>
+        <v>1.44</v>
       </c>
       <c r="M39" t="n">
-        <v>3.74</v>
+        <v>4.7</v>
       </c>
       <c r="N39" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="O39" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="P39" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.8</v>
+        <v>6.25</v>
       </c>
       <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>1.22</v>
       </c>
-      <c r="S39" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.07</v>
-      </c>
       <c r="X39" t="n">
-        <v>5.85</v>
+        <v>3.88</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.39</v>
+        <v>1.77</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.86</v>
+        <v>2.14</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>2.88</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.94</v>
+        <v>3.4</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="M40" t="n">
         <v>3.57</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
-        <v>2.15</v>
+        <v>3.05</v>
       </c>
       <c r="P40" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U40" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W40" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45965.70833333334</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -856,7 +856,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -910,45 +910,45 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
         <v>2.22</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
         <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.43</v>
+        <v>4.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
         <v>3.5</v>
@@ -960,32 +960,32 @@
         <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '77']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -997,7 +997,7 @@
         <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AI4" t="n">
         <v>1.95</v>
@@ -1042,42 +1042,42 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q5" t="n">
         <v>3.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T5" t="n">
         <v>3.75</v>
@@ -1089,16 +1089,16 @@
         <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AA5" t="n">
         <v>5.45</v>
@@ -1110,7 +1110,7 @@
         <v>2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1119,14 +1119,14 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" t="n">
         <v>2.09</v>
@@ -1168,20 +1168,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '38', '52', '79']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1300,75 +1300,75 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="U7" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="X7" t="n">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1377,14 +1377,14 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '62']</t>
         </is>
       </c>
       <c r="AG7" t="n">
         <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" t="n">
         <v>2.62</v>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
         <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
         <v>1.33</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68', '81']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="AI8" t="n">
         <v>1.83</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3.22</v>
+        <v>3.92</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.25</v>
+        <v>3.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="T10" t="n">
-        <v>3.88</v>
+        <v>4.45</v>
       </c>
       <c r="U10" t="n">
         <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="X10" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.45</v>
+        <v>2.98</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45965.4375</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2.8</v>
       </c>
-      <c r="M11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.98</v>
-      </c>
       <c r="Z11" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>7</v>
+        <v>5.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45965.4375</v>
@@ -1968,28 +1968,28 @@
         <v>1.35</v>
       </c>
       <c r="O12" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
         <v>2.14</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
         <v>1.48</v>
@@ -2004,16 +2004,16 @@
         <v>1.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AC12" t="n">
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AI12" t="n">
         <v>4.5</v>
@@ -2097,28 +2097,28 @@
         <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="T13" t="n">
         <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
@@ -2133,13 +2133,13 @@
         <v>1.38</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>2.61</v>
       </c>
       <c r="AD13" t="n">
         <v>1.5</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AI13" t="n">
         <v>1.61</v>
@@ -2226,34 +2226,34 @@
         <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
         <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
         <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.85</v>
@@ -2262,16 +2262,16 @@
         <v>1.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.66</v>
+        <v>3.34</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
         <v>1.65</v>
@@ -2355,25 +2355,25 @@
         <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.83</v>
+        <v>6.26</v>
       </c>
       <c r="R15" t="n">
         <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
         <v>1.1</v>
@@ -2394,7 +2394,7 @@
         <v>6.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC15" t="n">
         <v>2.51</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AI15" t="n">
         <v>1.72</v>
@@ -2484,28 +2484,28 @@
         <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="T16" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
         <v>1.67</v>
@@ -2523,13 +2523,13 @@
         <v>6.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" t="n">
         <v>2.3</v>
@@ -2616,16 +2616,16 @@
         <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
         <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="T17" t="n">
         <v>3.38</v>
@@ -2634,13 +2634,13 @@
         <v>1.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
         <v>2.4</v>
@@ -2649,16 +2649,16 @@
         <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.6</v>
+        <v>4.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
         <v>1.44</v>
@@ -2742,28 +2742,28 @@
         <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.9</v>
+        <v>3.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
         <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="S18" t="n">
         <v>2.15</v>
       </c>
       <c r="T18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>1.22</v>
       </c>
       <c r="V18" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W18" t="n">
         <v>1.62</v>
@@ -2778,16 +2778,16 @@
         <v>1.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.05</v>
+        <v>6.5</v>
       </c>
       <c r="AB18" t="n">
         <v>1.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
         <v>1.95</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.26</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>10</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.62</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.14</v>
+        <v>2.31</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.62</v>
+        <v>2.31</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.05</v>
+        <v>2.34</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.28</v>
+        <v>2.81</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45965.61458333334</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.63</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>4.24</v>
+        <v>5.6</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>1.27</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>10</v>
       </c>
       <c r="P20" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.6</v>
+        <v>1.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.34</v>
+        <v>1.05</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.48</v>
+        <v>3.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.81</v>
+        <v>1.28</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45965.61458333334</v>
@@ -3129,34 +3129,34 @@
         <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
         <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="X21" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="Y21" t="n">
         <v>1.85</v>
@@ -3171,10 +3171,10 @@
         <v>1.15</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AI21" t="n">
         <v>1.72</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="O22" t="n">
-        <v>3.69</v>
+        <v>3.95</v>
       </c>
       <c r="P22" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S22" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="T22" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="U22" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="X22" t="n">
-        <v>2.41</v>
+        <v>2.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.5</v>
+        <v>3.09</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AA22" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45965.625</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.02</v>
+        <v>3.51</v>
       </c>
       <c r="M23" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T23" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="X23" t="n">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AA23" t="n">
-        <v>6.75</v>
+        <v>5.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45965.625</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z25" t="n">
         <v>1.95</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AA25" t="n">
-        <v>4</v>
+        <v>3.52</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>3.97</v>
       </c>
       <c r="O26" t="n">
         <v>2.88</v>
@@ -3804,10 +3804,10 @@
         <v>3.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
         <v>3.7</v>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -3933,10 +3933,10 @@
         <v>2.54</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA27" t="n">
         <v>4.4</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.03</v>
+        <v>2.13</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="O28" t="n">
-        <v>3.83</v>
+        <v>3.05</v>
       </c>
       <c r="P28" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="T28" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X28" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,13 +4093,13 @@
         <v>1.36</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="M29" t="n">
-        <v>3.19</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>2.96</v>
+        <v>3.73</v>
       </c>
       <c r="O29" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="P29" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>2.69</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>3.02</v>
+        <v>2.94</v>
       </c>
       <c r="U29" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V29" t="n">
         <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X29" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
         <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,13 +4219,13 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AJ29" t="n">
         <v>2.4</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="M30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" t="n">
-        <v>3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.93</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S30" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="T30" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="U30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
         <v>1.36</v>
       </c>
-      <c r="X30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>4.5</v>
+        <v>3.87</v>
       </c>
       <c r="O31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y31" t="n">
         <v>2.2</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>3.99</v>
       </c>
       <c r="N32" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="P32" t="n">
         <v>2.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S32" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="T32" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U32" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="X32" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="M33" t="n">
-        <v>6.5</v>
+        <v>3.57</v>
       </c>
       <c r="N33" t="n">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="O33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y33" t="n">
         <v>1.7</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="Z33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="N34" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="O34" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T34" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U34" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
         <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AC34" t="n">
         <v>1.36</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="N35" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.8</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="T35" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z35" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R35" t="n">
+      <c r="AA35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.35</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="Y35" t="n">
+      <c r="AD35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI35" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AJ35" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="N36" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O36" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P36" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R36" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="S36" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U36" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
         <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.97</v>
+        <v>2.45</v>
       </c>
       <c r="AA36" t="n">
         <v>1.95</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AC36" t="n">
         <v>1.36</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="N37" t="n">
-        <v>5.54</v>
+        <v>3.81</v>
       </c>
       <c r="O37" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.35</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="T37" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
         <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="X37" t="n">
-        <v>4.33</v>
+        <v>3.78</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="N38" t="n">
-        <v>3.03</v>
+        <v>7.1</v>
       </c>
       <c r="O38" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="P38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AH38" t="n">
         <v>2.7</v>
       </c>
-      <c r="Q38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X38" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AI38" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,80 +5442,80 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="M39" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="N39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q39" t="n">
         <v>7.5</v>
       </c>
-      <c r="O39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>6.25</v>
-      </c>
       <c r="R39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.33</v>
       </c>
       <c r="AJ39" t="n">
         <v>3.4</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="O40" t="n">
         <v>3.05</v>
@@ -5610,10 +5610,10 @@
         <v>4.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
         <v>2.49</v>

--- a/jogos_2025-11-04.xlsx
+++ b/jogos_2025-11-04.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK40"/>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,91 +901,91 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['43', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45965.375</v>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,65 +1185,65 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>6.1</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.5</v>
+        <v>4.52</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>2.47</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>2.58</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.06</v>
+        <v>1.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.62</v>
+        <v>4.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['20', '38', '52', '79']</t>
+          <t>['43', '77']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.96</v>
+        <v>1.51</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45965.38541666666</v>
+        <v>45965.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,86 +1314,86 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.38</v>
       </c>
-      <c r="O7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AC7" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
+          <t>['20', '38', '52', '79']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['32', '62']</t>
-        </is>
-      </c>
       <c r="AG7" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.62</v>
+        <v>1.45</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45965.39583333334</v>
+        <v>45965.38541666666</v>
       </c>
     </row>
     <row r="8">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,86 +1572,86 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>3.45</v>
+        <v>1.38</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '62']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45965.41666666666</v>
+        <v>45965.39583333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1697,90 +1697,90 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
         <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45965.4375</v>
+        <v>45965.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1826,87 +1826,87 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3.92</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.73</v>
+        <v>3.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="S11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>2.3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45965.4375</v>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,112 +1933,112 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>2.58</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="N12" t="n">
-        <v>1.35</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
-        <v>11.5</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.14</v>
+        <v>4.73</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="U12" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="V12" t="n">
         <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="X12" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.95</v>
+        <v>5.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '45+2']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="AI12" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45965.5</v>
+        <v>45965.4375</v>
       </c>
     </row>
     <row r="13">
@@ -2071,94 +2071,94 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="M13" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="P13" t="n">
         <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="T13" t="n">
         <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="AI13" t="n">
         <v>1.61</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,87 +2191,87 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>9.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>1.42</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.65</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
         <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.34</v>
+        <v>5.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2280,23 +2280,23 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '36']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45965.54166666666</v>
+        <v>45965.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,112 +2320,112 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>1.27</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.26</v>
+        <v>3.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W15" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="X15" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.21</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA15" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.51</v>
+        <v>1.77</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>['31', '87']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45965.60416666666</v>
+        <v>45965.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.95</v>
+        <v>3.09</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S16" t="n">
         <v>2.12</v>
       </c>
       <c r="T16" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="X16" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="Z16" t="n">
         <v>1.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.4</v>
+        <v>6.65</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.15</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2600,87 +2600,87 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="N17" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.05</v>
+        <v>2.69</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S17" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="T17" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.28</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,87 +2729,87 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="M18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N18" t="n">
         <v>2.8</v>
       </c>
-      <c r="N18" t="n">
-        <v>3.15</v>
-      </c>
       <c r="O18" t="n">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.15</v>
-      </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.42</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45965.60416666666</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,112 +2836,112 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.05</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.34</v>
-      </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="R19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.25</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.6</v>
-      </c>
       <c r="V19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['4', '61', '73', '89']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
         <v>1.02</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH19" t="n">
-        <v>2.34</v>
+        <v>2.76</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.81</v>
+        <v>3.75</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45965.61458333334</v>
+        <v>45965.60416666666</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>5.6</v>
+        <v>4.21</v>
       </c>
       <c r="N20" t="n">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>10</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q20" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.62</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="Z20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.53</v>
       </c>
-      <c r="V20" t="n">
-        <v>1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.05</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>3.75</v>
+        <v>1.48</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.28</v>
+        <v>2.81</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45965.61458333334</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,112 +3094,112 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.18</v>
+        <v>12</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>1.26</v>
       </c>
       <c r="O21" t="n">
-        <v>2.63</v>
+        <v>10</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>1.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['32', '46', '68']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.15</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.93</v>
+        <v>1.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.72</v>
+        <v>3.75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.6</v>
+        <v>1.28</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45965.625</v>
+        <v>45965.61458333334</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O22" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S22" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="T22" t="n">
-        <v>4.4</v>
+        <v>3.84</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.15</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AC22" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45965.625</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.51</v>
+        <v>2.88</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="S23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI23" t="n">
         <v>2.3</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45965.625</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>7.6</v>
+        <v>3.95</v>
       </c>
       <c r="O24" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.5</v>
+        <v>4.84</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,19 +3574,19 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45965.66666666666</v>
+        <v>45965.625</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.23</v>
+        <v>1.52</v>
       </c>
       <c r="M25" t="n">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>3.07</v>
+        <v>5.5</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>1.98</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.93</v>
+        <v>6.09</v>
       </c>
       <c r="R25" t="n">
         <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X25" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,19 +3703,19 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.84</v>
+        <v>1.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.14</v>
+        <v>3.1</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45965.69791666666</v>
+        <v>45965.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,37 +3765,37 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3.17</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.08</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T26" t="n">
         <v>2.85</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
         <v>1.32</v>
@@ -3804,22 +3804,22 @@
         <v>3.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,13 +3835,13 @@
         <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45965.69791666666</v>
@@ -3897,25 +3897,25 @@
         <v>2.68</v>
       </c>
       <c r="M27" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="N27" t="n">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="R27" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="T27" t="n">
         <v>3.27</v>
@@ -3924,31 +3924,31 @@
         <v>1.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X27" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AA27" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
         <v>1.9</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.13</v>
+        <v>2.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2.96</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
-        <v>3.05</v>
+        <v>3.93</v>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S28" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T28" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X28" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N29" t="n">
-        <v>3.73</v>
+        <v>3.05</v>
       </c>
       <c r="O29" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
         <v>2</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
         <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,13 +4219,13 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AJ29" t="n">
         <v>2.4</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.91</v>
+        <v>1.7</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
-        <v>2.48</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.83</v>
+        <v>2.2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="T30" t="n">
-        <v>3.21</v>
+        <v>2.85</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="X30" t="n">
-        <v>2.89</v>
+        <v>3.44</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.54</v>
+        <v>2.99</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>3.87</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="P31" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="R31" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="V31" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W31" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="X31" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="M32" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>3.93</v>
       </c>
       <c r="O32" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="P32" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S32" t="n">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="T32" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X32" t="n">
         <v>2.9</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.4</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.05</v>
+        <v>3.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AD32" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45965.69791666666</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="M33" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.2</v>
+        <v>2.85</v>
       </c>
       <c r="P33" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.35</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>3.34</v>
+        <v>2.87</v>
       </c>
       <c r="T33" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="U33" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="X33" t="n">
-        <v>4.33</v>
+        <v>2.99</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>3.54</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,19 +4735,19 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45965.70833333334</v>
+        <v>45965.69791666666</v>
       </c>
     </row>
     <row r="34">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="P34" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI34" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45965.70833333334</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.79</v>
+        <v>7.5</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="P35" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>6.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S35" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.01</v>
+        <v>2.45</v>
       </c>
       <c r="U35" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X35" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.95</v>
+        <v>2.82</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.35</v>
+        <v>1.93</v>
       </c>
       <c r="AD35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH35" t="n">
         <v>3</v>
       </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AI35" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,62 +5055,62 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="M36" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="O36" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD36" t="n">
         <v>2.1</v>
       </c>
-      <c r="U36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X36" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,58 +5184,58 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.61</v>
+        <v>4.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3.81</v>
+        <v>5.83</v>
       </c>
       <c r="O37" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>5.47</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="V37" t="n">
         <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>3.78</v>
+        <v>4.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AD37" t="n">
         <v>2.1</v>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.39</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="N38" t="n">
-        <v>7.1</v>
+        <v>2.31</v>
       </c>
       <c r="O38" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.25</v>
+        <v>3.04</v>
       </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S38" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="U38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH38" t="n">
         <v>1.53</v>
       </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AI38" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AJ38" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.26</v>
+        <v>2.35</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="N39" t="n">
-        <v>9.5</v>
+        <v>2.68</v>
       </c>
       <c r="O39" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="P39" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.57</v>
+        <v>2.91</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.97</v>
+        <v>1.36</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>3.82</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.4</v>
+        <v>1.94</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45965.70833333334</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,85 +5571,214 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="M40" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>2.61</v>
+        <v>3.08</v>
       </c>
       <c r="O40" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="P40" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK40" s="3" t="n">
+        <v>45965.70833333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N41" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X41" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.3</v>
       </c>
-      <c r="S40" t="n">
+      <c r="AJ41" t="n">
         <v>3.4</v>
       </c>
-      <c r="T40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X40" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AK40" s="3" t="n">
+      <c r="AK41" s="3" t="n">
         <v>45965.70833333334</v>
       </c>
     </row>
